--- a/plot/data/source_data/source_data_fig_2_d.xlsx
+++ b/plot/data/source_data/source_data_fig_2_d.xlsx
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E281"/>
+  <dimension ref="A1:F281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -579,6 +579,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -607,6 +608,11 @@
           <t>score</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>score_scale</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -632,6 +638,11 @@
       <c r="E2" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -655,7 +666,12 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.25</v>
+        <v>4.463541666666667</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -682,6 +698,11 @@
       <c r="E4" s="2" t="n">
         <v>4.904761904761904</v>
       </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -705,7 +726,12 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.291666666666667</v>
+        <v>4.510416666666667</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -732,6 +758,11 @@
       <c r="E6" s="2" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -755,7 +786,12 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4.333333333333333</v>
+        <v>4.557291666666667</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -782,6 +818,11 @@
       <c r="E8" s="2" t="n">
         <v>4.61904761904762</v>
       </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -805,7 +846,12 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.104166666666667</v>
+        <v>4.322916666666667</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -832,6 +878,11 @@
       <c r="E10" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -855,7 +906,12 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>4.270833333333333</v>
+        <v>4.489583333333333</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -882,6 +938,11 @@
       <c r="E12" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -905,7 +966,12 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>4.229166666666667</v>
+        <v>4.442708333333333</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -932,6 +998,11 @@
       <c r="E14" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -955,7 +1026,12 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>4.270833333333333</v>
+        <v>4.489583333333333</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -982,6 +1058,11 @@
       <c r="E16" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1005,7 +1086,12 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>4.229166666666667</v>
+        <v>4.442708333333333</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1032,6 +1118,11 @@
       <c r="E18" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1055,7 +1146,12 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>4.25</v>
+        <v>4.463541666666667</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1082,6 +1178,11 @@
       <c r="E20" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1105,7 +1206,12 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>4.229166666666667</v>
+        <v>4.442708333333333</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1132,6 +1238,11 @@
       <c r="E22" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1155,7 +1266,12 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>4.291666666666667</v>
+        <v>4.510416666666667</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1182,6 +1298,11 @@
       <c r="E24" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1205,7 +1326,12 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>4.333333333333333</v>
+        <v>4.552083333333333</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1232,6 +1358,11 @@
       <c r="E26" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1255,7 +1386,12 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>4.333333333333333</v>
+        <v>4.557291666666667</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1282,6 +1418,11 @@
       <c r="E28" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1305,7 +1446,12 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>4.333333333333333</v>
+        <v>4.557291666666667</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1332,6 +1478,11 @@
       <c r="E30" s="2" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1355,7 +1506,12 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>4.25</v>
+        <v>4.479166666666667</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1382,6 +1538,11 @@
       <c r="E32" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1405,7 +1566,12 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>4.25</v>
+        <v>4.479166666666667</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -1432,6 +1598,11 @@
       <c r="E34" s="2" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1455,7 +1626,12 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>4.270833333333333</v>
+        <v>4.5</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -1482,6 +1658,11 @@
       <c r="E36" s="2" t="n">
         <v>4.904761904761904</v>
       </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1505,7 +1686,12 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>4.229166666666667</v>
+        <v>4.458333333333333</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -1532,6 +1718,11 @@
       <c r="E38" s="2" t="n">
         <v>4.095238095238096</v>
       </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1555,7 +1746,12 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>3.895833333333333</v>
+        <v>4.125</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -1582,6 +1778,11 @@
       <c r="E40" s="2" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1605,7 +1806,12 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>4</v>
+        <v>4.203125</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -1632,6 +1838,11 @@
       <c r="E42" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1655,7 +1866,12 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>4</v>
+        <v>4.203125</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -1682,6 +1898,11 @@
       <c r="E44" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1705,7 +1926,12 @@
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>4</v>
+        <v>4.208333333333333</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -1732,6 +1958,11 @@
       <c r="E46" s="2" t="n">
         <v>4.857142857142857</v>
       </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1755,7 +1986,12 @@
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>3.979166666666667</v>
+        <v>4.1875</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -1782,6 +2018,11 @@
       <c r="E48" s="2" t="n">
         <v>4.714285714285714</v>
       </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1805,7 +2046,12 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>4.041666666666667</v>
+        <v>4.25</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -1832,6 +2078,11 @@
       <c r="E50" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1855,7 +2106,12 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>4.020833333333333</v>
+        <v>4.229166666666667</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -1882,6 +2138,11 @@
       <c r="E52" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1905,7 +2166,12 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>4.270833333333333</v>
+        <v>4.494791666666667</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -1932,6 +2198,11 @@
       <c r="E54" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1955,7 +2226,12 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>4.041666666666667</v>
+        <v>4.25</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -1982,6 +2258,11 @@
       <c r="E56" s="2" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2005,7 +2286,12 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>4.354166666666667</v>
+        <v>4.583333333333333</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -2032,6 +2318,11 @@
       <c r="E58" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2055,7 +2346,12 @@
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>4.041666666666667</v>
+        <v>4.255208333333333</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -2082,6 +2378,11 @@
       <c r="E60" s="2" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2105,7 +2406,12 @@
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>4.291666666666667</v>
+        <v>4.515625</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -2132,6 +2438,11 @@
       <c r="E62" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2155,7 +2466,12 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>3.979166666666667</v>
+        <v>4.1875</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -2182,6 +2498,11 @@
       <c r="E64" s="2" t="n">
         <v>4.904761904761904</v>
       </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2205,7 +2526,12 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>3.979166666666667</v>
+        <v>4.1875</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -2232,6 +2558,11 @@
       <c r="E66" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2255,7 +2586,12 @@
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>4.208333333333333</v>
+        <v>4.416666666666667</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -2282,6 +2618,11 @@
       <c r="E68" s="2" t="n">
         <v>4.904761904761904</v>
       </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2305,7 +2646,12 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>4.104166666666667</v>
+        <v>4.3125</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -2332,6 +2678,11 @@
       <c r="E70" s="2" t="n">
         <v>4.904761904761904</v>
       </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2355,7 +2706,12 @@
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>4.3125</v>
+        <v>4.536458333333333</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -2382,6 +2738,11 @@
       <c r="E72" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2405,7 +2766,12 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>4.083333333333333</v>
+        <v>4.286458333333333</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -2432,6 +2798,11 @@
       <c r="E74" s="2" t="n">
         <v>4.904761904761905</v>
       </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2455,7 +2826,12 @@
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>4.0625</v>
+        <v>4.291666666666667</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -2482,6 +2858,11 @@
       <c r="E76" s="2" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2505,7 +2886,12 @@
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>4.1875</v>
+        <v>4.411458333333333</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -2532,6 +2918,11 @@
       <c r="E78" s="2" t="n">
         <v>4.857142857142857</v>
       </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2555,7 +2946,12 @@
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>4.083333333333333</v>
+        <v>4.307291666666667</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -2582,6 +2978,11 @@
       <c r="E80" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -2605,7 +3006,12 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>4.1875</v>
+        <v>4.411458333333333</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -2632,6 +3038,11 @@
       <c r="E82" s="2" t="n">
         <v>4.857142857142857</v>
       </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -2655,7 +3066,12 @@
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>4.145833333333333</v>
+        <v>4.375</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -2682,6 +3098,11 @@
       <c r="E84" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -2705,7 +3126,12 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>4.145833333333333</v>
+        <v>4.369791666666667</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -2732,6 +3158,11 @@
       <c r="E86" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -2755,7 +3186,12 @@
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>4.125</v>
+        <v>4.354166666666667</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -2782,6 +3218,11 @@
       <c r="E88" s="2" t="n">
         <v>4.904761904761904</v>
       </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -2805,7 +3246,12 @@
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>4.364583333333333</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -2832,6 +3278,11 @@
       <c r="E90" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -2855,7 +3306,12 @@
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>4.208333333333333</v>
+        <v>4.411458333333333</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -2882,6 +3338,11 @@
       <c r="E92" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -2905,7 +3366,12 @@
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>4.229166666666667</v>
+        <v>4.4375</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -2932,6 +3398,11 @@
       <c r="E94" s="2" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -2955,7 +3426,12 @@
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>4.020833333333333</v>
+        <v>4.229166666666667</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -2982,6 +3458,11 @@
       <c r="E96" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -3005,7 +3486,12 @@
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>4.020833333333333</v>
+        <v>4.229166666666667</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -3032,6 +3518,11 @@
       <c r="E98" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -3055,7 +3546,12 @@
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>4.020833333333333</v>
+        <v>4.229166666666667</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -3082,6 +3578,11 @@
       <c r="E100" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -3105,7 +3606,12 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>4.1875</v>
+        <v>4.395833333333333</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -3132,6 +3638,11 @@
       <c r="E102" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -3155,7 +3666,12 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>4.229166666666667</v>
+        <v>4.442708333333333</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -3182,6 +3698,11 @@
       <c r="E104" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -3205,7 +3726,12 @@
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -3232,6 +3758,11 @@
       <c r="E106" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -3255,7 +3786,12 @@
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>4.348958333333333</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -3282,6 +3818,11 @@
       <c r="E108" s="2" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -3305,7 +3846,12 @@
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>3.875</v>
+        <v>4.078125</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -3332,6 +3878,11 @@
       <c r="E110" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -3355,7 +3906,12 @@
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>4.041666666666667</v>
+        <v>4.255208333333333</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -3382,6 +3938,11 @@
       <c r="E112" s="2" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -3405,7 +3966,12 @@
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>3.895833333333333</v>
+        <v>4.088541666666667</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -3432,6 +3998,11 @@
       <c r="E114" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -3455,7 +4026,12 @@
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>4.104166666666667</v>
+        <v>4.302083333333333</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -3482,6 +4058,11 @@
       <c r="E116" s="2" t="n">
         <v>4.904761904761904</v>
       </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -3505,7 +4086,12 @@
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>4.041666666666667</v>
+        <v>4.25</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -3532,6 +4118,11 @@
       <c r="E118" s="2" t="n">
         <v>4.904761904761904</v>
       </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -3555,7 +4146,12 @@
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>4.020833333333333</v>
+        <v>4.229166666666667</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -3582,6 +4178,11 @@
       <c r="E120" s="2" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -3605,7 +4206,12 @@
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>4.125</v>
+        <v>4.338541666666667</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -3632,6 +4238,11 @@
       <c r="E122" s="2" t="n">
         <v>4.857142857142857</v>
       </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -3655,7 +4266,12 @@
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>4</v>
+        <v>4.213541666666667</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -3682,6 +4298,11 @@
       <c r="E124" s="2" t="n">
         <v>4.857142857142857</v>
       </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -3705,7 +4326,12 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>3.6875</v>
+        <v>3.885416666666667</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -3732,6 +4358,11 @@
       <c r="E126" s="2" t="n">
         <v>4.904761904761904</v>
       </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -3755,7 +4386,12 @@
         </is>
       </c>
       <c r="E127" s="2" t="n">
-        <v>3.895833333333333</v>
+        <v>4.09375</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -3782,6 +4418,11 @@
       <c r="E128" s="2" t="n">
         <v>4.904761904761904</v>
       </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -3805,7 +4446,12 @@
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>3.916666666666667</v>
+        <v>4.114583333333333</v>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -3832,6 +4478,11 @@
       <c r="E130" s="2" t="n">
         <v>4.904761904761904</v>
       </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -3855,7 +4506,12 @@
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>3.9375</v>
+        <v>4.135416666666667</v>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -3882,6 +4538,11 @@
       <c r="E132" s="2" t="n">
         <v>4.666666666666667</v>
       </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -3905,7 +4566,12 @@
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>3.645833333333333</v>
+        <v>3.838541666666667</v>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -3932,6 +4598,11 @@
       <c r="E134" s="2" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -3955,7 +4626,12 @@
         </is>
       </c>
       <c r="E135" s="2" t="n">
-        <v>3.854166666666667</v>
+        <v>4.052083333333333</v>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -3982,6 +4658,11 @@
       <c r="E136" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -4005,7 +4686,12 @@
         </is>
       </c>
       <c r="E137" s="2" t="n">
-        <v>4.020833333333333</v>
+        <v>4.239583333333333</v>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -4032,6 +4718,11 @@
       <c r="E138" s="2" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -4055,7 +4746,12 @@
         </is>
       </c>
       <c r="E139" s="2" t="n">
-        <v>3.895833333333333</v>
+        <v>4.098958333333333</v>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -4082,6 +4778,11 @@
       <c r="E140" s="2" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -4105,7 +4806,12 @@
         </is>
       </c>
       <c r="E141" s="2" t="n">
-        <v>3.9375</v>
+        <v>4.140625</v>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -4132,6 +4838,11 @@
       <c r="E142" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -4155,7 +4866,12 @@
         </is>
       </c>
       <c r="E143" s="2" t="n">
-        <v>4.3125</v>
+        <v>4.53125</v>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -4182,6 +4898,11 @@
       <c r="E144" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -4205,7 +4926,12 @@
         </is>
       </c>
       <c r="E145" s="2" t="n">
-        <v>4.3125</v>
+        <v>4.536458333333333</v>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -4232,6 +4958,11 @@
       <c r="E146" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -4255,7 +4986,12 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>4.125</v>
+        <v>4.328125</v>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="148">
@@ -4282,6 +5018,11 @@
       <c r="E148" s="2" t="n">
         <v>4.809523809523809</v>
       </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -4305,7 +5046,12 @@
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>4.229166666666667</v>
+        <v>4.432291666666667</v>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="150">
@@ -4332,6 +5078,11 @@
       <c r="E150" s="2" t="n">
         <v>4.904761904761904</v>
       </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -4355,7 +5106,12 @@
         </is>
       </c>
       <c r="E151" s="2" t="n">
-        <v>4.270833333333333</v>
+        <v>4.479166666666667</v>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="152">
@@ -4382,6 +5138,11 @@
       <c r="E152" s="2" t="n">
         <v>4.857142857142857</v>
       </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -4405,7 +5166,12 @@
         </is>
       </c>
       <c r="E153" s="2" t="n">
-        <v>4.333333333333333</v>
+        <v>4.557291666666667</v>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="154">
@@ -4432,6 +5198,11 @@
       <c r="E154" s="2" t="n">
         <v>4.904761904761904</v>
       </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -4455,7 +5226,12 @@
         </is>
       </c>
       <c r="E155" s="2" t="n">
-        <v>4.333333333333333</v>
+        <v>4.557291666666667</v>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="156">
@@ -4482,6 +5258,11 @@
       <c r="E156" s="2" t="n">
         <v>4.904761904761904</v>
       </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -4505,7 +5286,12 @@
         </is>
       </c>
       <c r="E157" s="2" t="n">
-        <v>4.291666666666667</v>
+        <v>4.510416666666667</v>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="158">
@@ -4532,6 +5318,11 @@
       <c r="E158" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -4555,7 +5346,12 @@
         </is>
       </c>
       <c r="E159" s="2" t="n">
-        <v>4.354166666666667</v>
+        <v>4.583333333333333</v>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="160">
@@ -4582,6 +5378,11 @@
       <c r="E160" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -4605,7 +5406,12 @@
         </is>
       </c>
       <c r="E161" s="2" t="n">
-        <v>4.354166666666667</v>
+        <v>4.583333333333333</v>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="162">
@@ -4632,6 +5438,11 @@
       <c r="E162" s="2" t="n">
         <v>4.904761904761904</v>
       </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -4655,7 +5466,12 @@
         </is>
       </c>
       <c r="E163" s="2" t="n">
-        <v>4.333333333333333</v>
+        <v>4.557291666666667</v>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="164">
@@ -4682,6 +5498,11 @@
       <c r="E164" s="2" t="n">
         <v>4.904761904761904</v>
       </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -4705,7 +5526,12 @@
         </is>
       </c>
       <c r="E165" s="2" t="n">
-        <v>4.125</v>
+        <v>4.333333333333333</v>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="166">
@@ -4732,6 +5558,11 @@
       <c r="E166" s="2" t="n">
         <v>4.904761904761904</v>
       </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -4755,7 +5586,12 @@
         </is>
       </c>
       <c r="E167" s="2" t="n">
-        <v>4.125</v>
+        <v>4.333333333333333</v>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="168">
@@ -4782,6 +5618,11 @@
       <c r="E168" s="2" t="n">
         <v>4.904761904761904</v>
       </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -4805,7 +5646,12 @@
         </is>
       </c>
       <c r="E169" s="2" t="n">
-        <v>4.125</v>
+        <v>4.333333333333333</v>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="170">
@@ -4832,6 +5678,11 @@
       <c r="E170" s="2" t="n">
         <v>4.904761904761905</v>
       </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -4855,7 +5706,12 @@
         </is>
       </c>
       <c r="E171" s="2" t="n">
-        <v>4.083333333333333</v>
+        <v>4.296875</v>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="172">
@@ -4882,6 +5738,11 @@
       <c r="E172" s="2" t="n">
         <v>4.904761904761905</v>
       </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -4905,7 +5766,12 @@
         </is>
       </c>
       <c r="E173" s="2" t="n">
-        <v>4.083333333333333</v>
+        <v>4.296875</v>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="174">
@@ -4932,6 +5798,11 @@
       <c r="E174" s="2" t="n">
         <v>4.904761904761905</v>
       </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -4955,7 +5826,12 @@
         </is>
       </c>
       <c r="E175" s="2" t="n">
-        <v>4.125</v>
+        <v>4.338541666666667</v>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="176">
@@ -4982,6 +5858,11 @@
       <c r="E176" s="2" t="n">
         <v>4.904761904761905</v>
       </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -5005,7 +5886,12 @@
         </is>
       </c>
       <c r="E177" s="2" t="n">
-        <v>4.125</v>
+        <v>4.338541666666667</v>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="178">
@@ -5032,6 +5918,11 @@
       <c r="E178" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -5055,7 +5946,12 @@
         </is>
       </c>
       <c r="E179" s="2" t="n">
-        <v>4.270833333333333</v>
+        <v>4.494791666666667</v>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="180">
@@ -5082,6 +5978,11 @@
       <c r="E180" s="2" t="n">
         <v>4.904761904761905</v>
       </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -5105,7 +6006,12 @@
         </is>
       </c>
       <c r="E181" s="2" t="n">
-        <v>4.291666666666667</v>
+        <v>4.515625</v>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="182">
@@ -5132,6 +6038,11 @@
       <c r="E182" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -5155,7 +6066,12 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>4.416666666666667</v>
+        <v>4.640625</v>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="184">
@@ -5182,6 +6098,11 @@
       <c r="E184" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -5205,7 +6126,12 @@
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>4.354166666666667</v>
+        <v>4.578125</v>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="186">
@@ -5232,6 +6158,11 @@
       <c r="E186" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -5255,7 +6186,12 @@
         </is>
       </c>
       <c r="E187" s="2" t="n">
-        <v>4.395833333333333</v>
+        <v>4.619791666666667</v>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="188">
@@ -5282,6 +6218,11 @@
       <c r="E188" s="2" t="n">
         <v>4.857142857142857</v>
       </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -5305,7 +6246,12 @@
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>4.3125</v>
+        <v>4.541666666666667</v>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="190">
@@ -5332,6 +6278,11 @@
       <c r="E190" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -5355,7 +6306,12 @@
         </is>
       </c>
       <c r="E191" s="2" t="n">
-        <v>4.375</v>
+        <v>4.609375</v>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="192">
@@ -5382,6 +6338,11 @@
       <c r="E192" s="2" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -5405,7 +6366,12 @@
         </is>
       </c>
       <c r="E193" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="194">
@@ -5432,6 +6398,11 @@
       <c r="E194" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -5455,7 +6426,12 @@
         </is>
       </c>
       <c r="E195" s="2" t="n">
-        <v>4.333333333333333</v>
+        <v>4.546875</v>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="196">
@@ -5482,6 +6458,11 @@
       <c r="E196" s="2" t="n">
         <v>4.809523809523809</v>
       </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -5505,7 +6486,12 @@
         </is>
       </c>
       <c r="E197" s="2" t="n">
-        <v>4.291666666666667</v>
+        <v>4.515625</v>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="198">
@@ -5532,6 +6518,11 @@
       <c r="E198" s="2" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -5555,7 +6546,12 @@
         </is>
       </c>
       <c r="E199" s="2" t="n">
-        <v>4.083333333333333</v>
+        <v>4.296875</v>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="200">
@@ -5582,6 +6578,11 @@
       <c r="E200" s="2" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -5605,7 +6606,12 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>4.104166666666667</v>
+        <v>4.317708333333333</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="202">
@@ -5632,6 +6638,11 @@
       <c r="E202" t="n">
         <v>5</v>
       </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -5655,7 +6666,12 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>4.291666666666667</v>
+        <v>4.515625</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="204">
@@ -5682,6 +6698,11 @@
       <c r="E204" t="n">
         <v>5</v>
       </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5705,7 +6726,12 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4</v>
+        <v>4.213541666666667</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="206">
@@ -5732,6 +6758,11 @@
       <c r="E206" t="n">
         <v>5</v>
       </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -5755,7 +6786,12 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>4.041666666666667</v>
+        <v>4.25</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="208">
@@ -5782,6 +6818,11 @@
       <c r="E208" t="n">
         <v>5</v>
       </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -5805,7 +6846,12 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4.125</v>
+        <v>4.34375</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="210">
@@ -5832,6 +6878,11 @@
       <c r="E210" t="n">
         <v>5</v>
       </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -5855,7 +6906,12 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>4.375</v>
+        <v>4.609375</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="212">
@@ -5882,6 +6938,11 @@
       <c r="E212" t="n">
         <v>5</v>
       </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -5905,7 +6966,12 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>4.125</v>
+        <v>4.348958333333333</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="214">
@@ -5932,6 +6998,11 @@
       <c r="E214" t="n">
         <v>5</v>
       </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -5955,7 +7026,12 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>4.041666666666667</v>
+        <v>4.255208333333333</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="216">
@@ -5982,6 +7058,11 @@
       <c r="E216" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -6005,7 +7086,12 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>3.895833333333333</v>
+        <v>4.088541666666667</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="218">
@@ -6032,6 +7118,11 @@
       <c r="E218" t="n">
         <v>5</v>
       </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -6055,7 +7146,12 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>4.083333333333333</v>
+        <v>4.291666666666667</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="220">
@@ -6082,6 +7178,11 @@
       <c r="E220" t="n">
         <v>4.571428571428572</v>
       </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -6105,7 +7206,12 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>4.104166666666667</v>
+        <v>4.317708333333333</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="222">
@@ -6132,6 +7238,11 @@
       <c r="E222" t="n">
         <v>4.904761904761905</v>
       </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -6155,7 +7266,12 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>4.208333333333333</v>
+        <v>4.432291666666667</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="224">
@@ -6182,6 +7298,11 @@
       <c r="E224" t="n">
         <v>5</v>
       </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -6205,7 +7326,12 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>4.104166666666667</v>
+        <v>4.328125</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="226">
@@ -6232,6 +7358,11 @@
       <c r="E226" t="n">
         <v>4.904761904761905</v>
       </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -6255,7 +7386,12 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>4.166666666666667</v>
+        <v>4.390625</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="228">
@@ -6282,6 +7418,11 @@
       <c r="E228" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -6305,7 +7446,12 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>4.270833333333333</v>
+        <v>4.479166666666667</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="230">
@@ -6332,6 +7478,11 @@
       <c r="E230" t="n">
         <v>5</v>
       </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -6355,7 +7506,12 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>4.270833333333333</v>
+        <v>4.479166666666667</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="232">
@@ -6382,6 +7538,11 @@
       <c r="E232" t="n">
         <v>5</v>
       </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -6405,7 +7566,12 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>4.166666666666667</v>
+        <v>4.369791666666667</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="234">
@@ -6432,6 +7598,11 @@
       <c r="E234" t="n">
         <v>5</v>
       </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -6455,7 +7626,12 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>4.208333333333333</v>
+        <v>4.421875</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="236">
@@ -6482,6 +7658,11 @@
       <c r="E236" t="n">
         <v>5</v>
       </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -6505,7 +7686,12 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>4.208333333333333</v>
+        <v>4.421875</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="238">
@@ -6532,6 +7718,11 @@
       <c r="E238" t="n">
         <v>5</v>
       </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -6555,7 +7746,12 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>4.1875</v>
+        <v>4.401041666666667</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="240">
@@ -6582,6 +7778,11 @@
       <c r="E240" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -6605,7 +7806,12 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>3.958333333333333</v>
+        <v>4.171875</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="242">
@@ -6632,6 +7838,11 @@
       <c r="E242" t="n">
         <v>5</v>
       </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -6655,7 +7866,12 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>4.0625</v>
+        <v>4.28125</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="244">
@@ -6682,6 +7898,11 @@
       <c r="E244" t="n">
         <v>5</v>
       </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -6705,7 +7926,12 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>4.020833333333333</v>
+        <v>4.229166666666667</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="246">
@@ -6732,6 +7958,11 @@
       <c r="E246" t="n">
         <v>5</v>
       </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -6755,7 +7986,12 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>4.104166666666667</v>
+        <v>4.317708333333333</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="248">
@@ -6782,6 +8018,11 @@
       <c r="E248" t="n">
         <v>5</v>
       </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -6805,7 +8046,12 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>4.395833333333333</v>
+        <v>4.625</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="250">
@@ -6832,6 +8078,11 @@
       <c r="E250" t="n">
         <v>5</v>
       </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -6855,7 +8106,12 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>4.395833333333333</v>
+        <v>4.619791666666667</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="252">
@@ -6882,6 +8138,11 @@
       <c r="E252" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -6905,7 +8166,12 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>3.979166666666667</v>
+        <v>4.192708333333333</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="254">
@@ -6932,6 +8198,11 @@
       <c r="E254" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -6955,7 +8226,12 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>4.145833333333333</v>
+        <v>4.359375</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="256">
@@ -6982,6 +8258,11 @@
       <c r="E256" t="n">
         <v>5</v>
       </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -7005,7 +8286,12 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>4</v>
+        <v>4.213541666666667</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="258">
@@ -7032,6 +8318,11 @@
       <c r="E258" t="n">
         <v>5</v>
       </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -7055,7 +8346,12 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>4.020833333333333</v>
+        <v>4.234375</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="260">
@@ -7082,6 +8378,11 @@
       <c r="E260" t="n">
         <v>5</v>
       </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -7105,7 +8406,12 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>4.0625</v>
+        <v>4.286458333333333</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="262">
@@ -7132,6 +8438,11 @@
       <c r="E262" t="n">
         <v>5</v>
       </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -7155,7 +8466,12 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>4.0625</v>
+        <v>4.260416666666667</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="264">
@@ -7182,6 +8498,11 @@
       <c r="E264" t="n">
         <v>5</v>
       </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -7205,7 +8526,12 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>3.833333333333333</v>
+        <v>4.03125</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="266">
@@ -7232,6 +8558,11 @@
       <c r="E266" t="n">
         <v>5</v>
       </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -7255,7 +8586,12 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>4.125</v>
+        <v>4.338541666666667</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="268">
@@ -7282,6 +8618,11 @@
       <c r="E268" t="n">
         <v>5</v>
       </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -7305,7 +8646,12 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>4.020833333333333</v>
+        <v>4.21875</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="270">
@@ -7332,6 +8678,11 @@
       <c r="E270" t="n">
         <v>5</v>
       </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -7355,7 +8706,12 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>3.895833333333333</v>
+        <v>4.09375</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="272">
@@ -7382,6 +8738,11 @@
       <c r="E272" t="n">
         <v>5</v>
       </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -7405,7 +8766,12 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>4.041666666666667</v>
+        <v>4.25</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="274">
@@ -7432,6 +8798,11 @@
       <c r="E274" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -7455,7 +8826,12 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>4.020833333333333</v>
+        <v>4.213541666666667</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="276">
@@ -7482,6 +8858,11 @@
       <c r="E276" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -7505,7 +8886,12 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>3.916666666666667</v>
+        <v>4.119791666666667</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="278">
@@ -7532,6 +8918,11 @@
       <c r="E278" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -7555,7 +8946,12 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>3.9375</v>
+        <v>4.135416666666667</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
     <row r="280">
@@ -7582,6 +8978,11 @@
       <c r="E280" t="n">
         <v>4.952380952380953</v>
       </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -7605,7 +9006,12 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>3.9375</v>
+        <v>4.135416666666667</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>mean of component scores standardized to 5 points</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -7746,13 +9152,13 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.0999999999999992</v>
+        <v>0.09843750000000009</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.0061343867422789</v>
+        <v>0.0004363470716327</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.1938656132577194</v>
+        <v>0.1964386529283676</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>-0.25</v>
@@ -7824,13 +9230,13 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.0502450980392161</v>
+        <v>0.0591299019607838</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>-0.0342668776521369</v>
+        <v>-0.0267808618011855</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1347570737305692</v>
+        <v>0.1450406657227532</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>-0.25</v>
@@ -7902,13 +9308,13 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.1000000000000005</v>
+        <v>0.1031249999999994</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.0273363562801045</v>
+        <v>0.0269819032126934</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.1726636437198965</v>
+        <v>0.1792680967873055</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>-0.25</v>
@@ -7980,13 +9386,13 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-0.0393518518518529</v>
+        <v>-0.0439814814814809</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.0945462753976596</v>
+        <v>-0.102181092188314</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.0158425716939536</v>
+        <v>0.0142181292253521</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>-0.25</v>
